--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260212_202527.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260212_202527.xlsx
@@ -5068,7 +5068,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5302,7 +5302,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5458,7 +5458,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -7704,7 +7704,7 @@
       </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7780,7 +7780,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7856,7 +7856,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260212_202527.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260212_202527.xlsx
@@ -5684,7 +5684,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5824,7 +5824,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6206,7 +6206,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6362,7 +6362,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260212_202527.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260212_202527.xlsx
@@ -5068,7 +5068,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5302,7 +5302,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5458,7 +5458,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5684,7 +5684,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5824,7 +5824,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6206,7 +6206,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6362,7 +6362,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7704,7 +7704,7 @@
       </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7780,7 +7780,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7856,7 +7856,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260212_202527.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260212_202527.xlsx
@@ -5068,7 +5068,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5302,7 +5302,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5458,7 +5458,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5684,7 +5684,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5824,7 +5824,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6206,7 +6206,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6362,7 +6362,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7704,7 +7704,7 @@
       </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7780,7 +7780,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7856,7 +7856,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260212_202527.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260212_202527.xlsx
@@ -5684,7 +5684,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5824,7 +5824,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6206,7 +6206,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6362,7 +6362,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7704,7 +7704,7 @@
       </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7780,7 +7780,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7856,7 +7856,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260212_202527.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260212_202527.xlsx
@@ -7704,7 +7704,7 @@
       </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7780,7 +7780,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7856,7 +7856,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260212_202527.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260212_202527.xlsx
@@ -7704,7 +7704,7 @@
       </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7780,7 +7780,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7856,7 +7856,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260212_202527.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260212_202527.xlsx
@@ -5684,7 +5684,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5824,7 +5824,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6206,7 +6206,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6362,7 +6362,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260212_202527.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260212_202527.xlsx
@@ -5684,7 +5684,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5824,7 +5824,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6206,7 +6206,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6362,7 +6362,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7704,7 +7704,7 @@
       </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7780,7 +7780,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7856,7 +7856,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260212_202527.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260212_202527.xlsx
@@ -5068,7 +5068,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5302,7 +5302,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5458,7 +5458,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -7704,7 +7704,7 @@
       </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7780,7 +7780,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7856,7 +7856,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260212_202527.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260212_202527.xlsx
@@ -5068,7 +5068,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5302,7 +5302,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5458,7 +5458,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260212_202527.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260212_202527.xlsx
@@ -5068,7 +5068,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5302,7 +5302,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5458,7 +5458,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260212_202527.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260212_202527.xlsx
@@ -5068,7 +5068,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5302,7 +5302,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5458,7 +5458,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5684,7 +5684,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5824,7 +5824,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6206,7 +6206,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6362,7 +6362,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7704,7 +7704,7 @@
       </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7780,7 +7780,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7856,7 +7856,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260212_202527.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260212_202527.xlsx
@@ -5068,7 +5068,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5302,7 +5302,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5458,7 +5458,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5684,7 +5684,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5824,7 +5824,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6206,7 +6206,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6362,7 +6362,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7704,7 +7704,7 @@
       </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7780,7 +7780,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7856,7 +7856,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260212_202527.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260212_202527.xlsx
@@ -5068,7 +5068,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5302,7 +5302,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5458,7 +5458,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -7704,7 +7704,7 @@
       </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7780,7 +7780,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7856,7 +7856,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260212_202527.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260212_202527.xlsx
@@ -5068,7 +5068,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5302,7 +5302,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5458,7 +5458,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5684,7 +5684,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5824,7 +5824,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6206,7 +6206,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6362,7 +6362,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260212_202527.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260212_202527.xlsx
@@ -5068,7 +5068,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5302,7 +5302,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5458,7 +5458,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5684,7 +5684,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5824,7 +5824,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6206,7 +6206,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6362,7 +6362,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260212_202527.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260212_202527.xlsx
@@ -5068,7 +5068,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5302,7 +5302,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5458,7 +5458,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -7704,7 +7704,7 @@
       </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7780,7 +7780,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7856,7 +7856,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260212_202527.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260212_202527.xlsx
@@ -5068,7 +5068,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5302,7 +5302,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5458,7 +5458,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5684,7 +5684,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5824,7 +5824,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6206,7 +6206,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6362,7 +6362,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7704,7 +7704,7 @@
       </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7780,7 +7780,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7856,7 +7856,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260212_202527.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260212_202527.xlsx
@@ -5068,7 +5068,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5302,7 +5302,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5458,7 +5458,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5684,7 +5684,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5824,7 +5824,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6206,7 +6206,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6362,7 +6362,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260212_202527.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260212_202527.xlsx
@@ -5068,7 +5068,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5302,7 +5302,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5458,7 +5458,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5684,7 +5684,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5824,7 +5824,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6206,7 +6206,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6362,7 +6362,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260212_202527.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260212_202527.xlsx
@@ -5684,7 +5684,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5824,7 +5824,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6206,7 +6206,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6362,7 +6362,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7704,7 +7704,7 @@
       </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7780,7 +7780,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7856,7 +7856,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260212_202527.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260212_202527.xlsx
@@ -5684,7 +5684,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5824,7 +5824,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6206,7 +6206,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6362,7 +6362,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7704,7 +7704,7 @@
       </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7780,7 +7780,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7856,7 +7856,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260212_202527.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260212_202527.xlsx
@@ -5068,7 +5068,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5302,7 +5302,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5458,7 +5458,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5684,7 +5684,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5824,7 +5824,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6206,7 +6206,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6362,7 +6362,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7704,7 +7704,7 @@
       </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7780,7 +7780,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7856,7 +7856,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
